--- a/ailyn_project_ledger.xlsx
+++ b/ailyn_project_ledger.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Payroll" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Monthly Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Receipt Archive" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monthly Closing" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Payroll'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly Summary'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Receipt Archive'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Monthly Closing'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -709,4 +711,59 @@
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Closed At</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Closed By</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total Spending</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>